--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.19511582915443</v>
+        <v>6.044206322237596</v>
       </c>
       <c r="D2" t="n">
-        <v>36.81264919913141</v>
+        <v>5.982055494858854</v>
       </c>
       <c r="E2" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.05164689616862</v>
+        <v>6.508392620627401</v>
       </c>
       <c r="D3" t="n">
-        <v>39.59069777282705</v>
+        <v>6.433488388084395</v>
       </c>
       <c r="E3" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F3" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.48468817854219</v>
+        <v>5.278761829013106</v>
       </c>
       <c r="D4" t="n">
-        <v>32.04444335231489</v>
+        <v>5.207222044751169</v>
       </c>
       <c r="E4" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F4" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.50752640304481</v>
+        <v>3.982473040494782</v>
       </c>
       <c r="D5" t="n">
-        <v>24.24241516971018</v>
+        <v>3.939392465077905</v>
       </c>
       <c r="E5" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F5" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.51244433387753</v>
+        <v>7.395772204255099</v>
       </c>
       <c r="D6" t="n">
-        <v>45.14843997143233</v>
+        <v>7.336621495357754</v>
       </c>
       <c r="E6" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F6" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.12802996506794</v>
+        <v>4.89580486932354</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76291162831713</v>
+        <v>4.836473139601534</v>
       </c>
       <c r="E7" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F7" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.47565016433013</v>
+        <v>4.627293151703646</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37057302328188</v>
+        <v>4.610218116283306</v>
       </c>
       <c r="E8" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F8" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.20680340461129</v>
+        <v>3.283605553249334</v>
       </c>
       <c r="D9" t="n">
-        <v>20.55724647159423</v>
+        <v>3.340552551634063</v>
       </c>
       <c r="E9" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F9" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.568080766891185</v>
+        <v>1.392313124619818</v>
       </c>
       <c r="D10" t="n">
-        <v>8.773675165556339</v>
+        <v>1.425722214402905</v>
       </c>
       <c r="E10" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F10" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.57311764051963</v>
+        <v>7.08063161658444</v>
       </c>
       <c r="D11" t="n">
-        <v>43.64636315499906</v>
+        <v>7.092534012687347</v>
       </c>
       <c r="E11" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F11" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.67525470887525</v>
+        <v>5.797228890192229</v>
       </c>
       <c r="D12" t="n">
-        <v>35.86362731314847</v>
+        <v>5.827839438386627</v>
       </c>
       <c r="E12" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F12" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.84154251803543</v>
+        <v>5.499250659180758</v>
       </c>
       <c r="D13" t="n">
-        <v>33.80301059436859</v>
+        <v>5.492989221584897</v>
       </c>
       <c r="E13" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F13" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.588691693150942</v>
+        <v>1.395662400137028</v>
       </c>
       <c r="D14" t="n">
-        <v>7.778255535617324</v>
+        <v>1.263966524537815</v>
       </c>
       <c r="E14" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F14" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.63862009436128</v>
+        <v>5.953775765333708</v>
       </c>
       <c r="D15" t="n">
-        <v>35.80463225757665</v>
+        <v>5.818252741856206</v>
       </c>
       <c r="E15" t="n">
-        <v>11.08070238112977</v>
+        <v>1.800614136933588</v>
       </c>
       <c r="F15" t="n">
-        <v>11.0513563646176</v>
+        <v>1.795845409250361</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
